--- a/inspection_forms/029_swppp_inspection--inspection_forms.xlsx
+++ b/inspection_forms/029_swppp_inspection--inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,64 +520,76 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>swppp_inspection</t>
+          <t>site_location</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>swppp_inspection</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Site Location</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A brief description of the site location.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>site_location</t>
+          <t>swppp_runoff_source</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>site_location</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Stormwater Runoff Source</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Is stormwater runoff an issue at this site?</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>stormwater_runoff_source</t>
+          <t>swppp_compliance_frequency</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>stormwater_runoff_source</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Compliance Frequency</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>How often is the SWPPP inspected?</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,38 +601,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>swppp_compliance_frequency</t>
+          <t>swppp_responsible_party</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>swppp_compliance_frequency</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Responsible Party</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Who is responsible for SWPPP at this site?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>swppp_responsible_party</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>swppp_responsible_party</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Additional comments or notes.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,69 +650,81 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>swppp_inspection_date</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Inspection Date</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Date of last inspection.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>swppp_inspection_date</t>
+          <t>swppp_inspection_status</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>swppp_inspection_date</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Inspection Status</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Is the inspection active or inactive?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>swppp_compliance_certificate</t>
+          <t>swppp_inspection_last_updated</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>swppp_compliance_certificate</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Date of last update.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,133 +736,157 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>swppp_compliance_certificate_expiration</t>
+          <t>swppp_inspection_next_due_date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>swppp_compliance_certificate_expiration</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Next Due Date</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Date of next due inspection.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>swppp_inspection_status</t>
+          <t>swppp_inspection_last_inspection_date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>swppp_inspection_status</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Last Inspection Date</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Date of last inspection.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>swppp_inspection_last_updated</t>
+          <t>swppp_inspection_last_inspector</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>swppp_inspection_last_updated</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Last Inspector</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Name of last inspector.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>swppp_inspection_next_due_date</t>
+          <t>swppp_inspection_last_inspector_signature</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>swppp_inspection_next_due_date</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Last Inspector Signature</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Last inspector's signature.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>swppp_inspection_last_inspection_date</t>
+          <t>swppp_inspection_last_inspection_cost</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>swppp_inspection_last_inspection_date</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Last Inspection Cost</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Cost of last inspection.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>swppp_inspection_last_inspector</t>
+          <t>swppp_inspection_last_inspection_cost_currency</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>swppp_inspection_last_inspector</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Last Inspection Cost Currency</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Currency of last inspection cost.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,18 +898,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>swppp_inspection_last_inspector_signature</t>
+          <t>swppp_inspection_last_inspection_cost_amount</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>swppp_inspection_last_inspector_signature</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Last Inspection Cost Amount</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Amount of last inspection cost.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,41 +925,49 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>swppp_inspection_last_inspection_cost</t>
+          <t>swppp_inspection_last_inspector_notes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>swppp_inspection_last_inspection_cost</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Last Inspector Notes</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Notes from last inspector.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>swppp_inspection_last_inspection_cost_currency</t>
+          <t>swppp_inspection_last_inspector_signature_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>swppp_inspection_last_inspection_cost_currency</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Swppp Inspection Last Inspector Signature 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Last inspector's signature.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,177 +979,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>swppp_inspection_last_inspection_cost_other_currency</t>
+          <t>swppp_inspection_last_inspector_signature_2_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>swppp_inspection_last_inspection_cost_other_currency</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Swppp Inspection Last Inspector Signature 2 2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Last inspector's signature.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>swppp_inspection_last_inspection_cost_amount</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>swppp_inspection_last_inspection_cost_amount</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>swppp_inspection_last_inspector_notes</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>swppp_inspection_last_inspector_notes</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>swppp_inspection_last_inspector_notes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>swppp_inspection_last_inspector_notes</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>swppp_inspection_last_inspector_notes</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>swppp_inspection_last_inspector_notes</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>swppp_inspection_last_inspector_notes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>swppp_inspection_last_inspector_notes</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>swppp_inspection_last_inspector_signature</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>swppp_inspection_last_inspector_signature</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>swppp_inspection_last_inspector_signature</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>swppp_inspection_last_inspector_signature</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,8 +1013,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,34 +1037,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>stormwater_runoff_source_choices</t>
+          <t>swppp_runoff_source_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>stormwater_runoff_source_choices</t>
+          <t>swppp_runoff_source_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1076,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1093,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1110,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1127,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1144,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'semi-annual'}</t>
+          <t>semi-annually</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Semi-Annual'}</t>
+          <t>Semi-Annually</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1161,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1178,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'owner'}</t>
+          <t>owner</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Owner'}</t>
+          <t>Owner</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1195,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'operator'}</t>
+          <t>operator</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Operator'}</t>
+          <t>Operator</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1212,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1229,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1246,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1263,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1280,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'usd'}</t>
+          <t>usd</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'USD'}</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1297,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'eur'}</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'EUR'}</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1314,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
